--- a/data/trans_bre/BARTHEL_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Provincia-trans_bre.xlsx
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>-3,83</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-30,07</t>
+          <t>30,07</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,92</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,32</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>-38,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-35,56%</t>
+          <t>194,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-14,67%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,78%</t>
+          <t>125,12%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 15,72</t>
+          <t>-15,6; 9,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-47,94; -10,88</t>
+          <t>13,4; 47,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 7,6</t>
+          <t>-7,65; 30,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 1,12</t>
+          <t>-1,19; 16,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 19,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,51; -13,84</t>
+          <t>48,73; 572,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 10,94</t>
+          <t>-24,05; 196,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 1,23</t>
+          <t>-31,7; 804,4</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-9,38</t>
+          <t>9,38</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-17,95</t>
+          <t>17,95</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-15,84</t>
+          <t>15,84</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-15,61</t>
+          <t>15,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-9,82%</t>
+          <t>208,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,44%</t>
+          <t>110,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-16,9%</t>
+          <t>252,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-17,71%</t>
+          <t>131,25%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -0,59</t>
+          <t>0,92; 17,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,89; -3,23</t>
+          <t>2,79; 31,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,23; -5,8</t>
+          <t>5,98; 26,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,24; -6,13</t>
+          <t>6,72; 24,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -0,76</t>
+          <t>-20,04; 1140,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,39; -5,2</t>
+          <t>2,4; 346,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,48; -6,46</t>
+          <t>39,75; 752,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,41; -7,96</t>
+          <t>35,91; 379,98</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-7,52</t>
+          <t>7,52</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-6,12</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-7,98%</t>
+          <t>130,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,34%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-2,31%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,73%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 3,24</t>
+          <t>-1,31; 17,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 8,84</t>
+          <t>-8,64; 20,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 7,47</t>
+          <t>-7,93; 13,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 8,8</t>
+          <t>-9,16; 11,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 3,52</t>
+          <t>-32,87; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 12,02</t>
+          <t>-37,04; 238,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 8,8</t>
+          <t>-70,53; 447,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 12,63</t>
+          <t>-30,63; 61,58</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-11,01</t>
+          <t>11,01</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10,07</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-5,32</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,79</t>
+          <t>10,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-11,55%</t>
+          <t>235,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,66%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-6,41%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,91%</t>
+          <t>115,23%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -1,9</t>
+          <t>1,36; 21,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 3,87</t>
+          <t>-3,89; 22,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 8,38</t>
+          <t>-7,17; 18,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,18; -2,99</t>
+          <t>2,37; 17,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,92; -1,96</t>
+          <t>-11,55; 1248,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 4,53</t>
+          <t>-20,77; 321,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 10,15</t>
+          <t>-30,94; 187,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -3,45</t>
+          <t>10,11; 293,96</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-8,06</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-18,34</t>
+          <t>18,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,5</t>
+          <t>5,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-4,23%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,23%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-19,07%</t>
+          <t>478,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-6,67%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 14,86</t>
+          <t>-15,64; 20,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 11,85</t>
+          <t>-11,96; 28,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,5; -6,24</t>
+          <t>5,71; 31,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 5,81</t>
+          <t>-6,15; 15,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 20,63</t>
+          <t>-60,98; 252,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,46; 16,82</t>
+          <t>-38,96; 305,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,9; -6,33</t>
+          <t>9,67; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 7,83</t>
+          <t>-25,62; 154,35</t>
         </is>
       </c>
     </row>
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-5,79</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-4,6</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,12</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-6,28%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,95%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>-15,28%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-13,13%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 5,63</t>
+          <t>-5,26; 17,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 12,25</t>
+          <t>-12,79; 19,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 5,43</t>
+          <t>-5,01; 27,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,83; -0,38</t>
+          <t>-0,58; 19,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 6,38</t>
+          <t>-48,96; 662,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 18,54</t>
+          <t>-40,86; 130,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 6,83</t>
+          <t>-20,58; 195,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,16; -0,46</t>
+          <t>-2,95; 114,53</t>
         </is>
       </c>
     </row>
@@ -1212,42 +1212,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-7,1</t>
+          <t>7,1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-13,83</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-0,02%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,32%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-15,91%</t>
+          <t>105,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>-19,21%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 4,82</t>
+          <t>-4,99; 5,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 5,25</t>
+          <t>-3,53; 16,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,4; -4,58</t>
+          <t>3,86; 23,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 15,39</t>
+          <t>-14,54; 15,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 5,13</t>
+          <t>-81,93; 479,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 6,66</t>
+          <t>-18,14; 176,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,46; -5,71</t>
+          <t>24,39; 282,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 19,21</t>
+          <t>-82,4; 146,38</t>
         </is>
       </c>
     </row>
@@ -1312,42 +1312,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-5,99</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>10,52</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,29</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-9,56</t>
+          <t>9,56</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-6,9%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-11,56%</t>
+          <t>116,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-4,72%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-10,48%</t>
+          <t>109,69%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 3,51</t>
+          <t>-2,59; 14,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -1,97</t>
+          <t>1,4; 19,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 3,64</t>
+          <t>-3,11; 12,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,62; -4,3</t>
+          <t>4,6; 15,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 4,23</t>
+          <t>-16,62; 189,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,24; -2,62</t>
+          <t>5,77; 376,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 4,22</t>
+          <t>-28,75; 258,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -4,87</t>
+          <t>32,36; 251,65</t>
         </is>
       </c>
     </row>
@@ -1412,42 +1412,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-5,52</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-10,98</t>
+          <t>10,98</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,84</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-5,99%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-12,9%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>-11,16%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-5,95%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -2,15</t>
+          <t>1,99; 8,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -5,99</t>
+          <t>6,58; 15,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -5,96</t>
+          <t>5,94; 14,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 3,32</t>
+          <t>-4,58; 10,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -2,31</t>
+          <t>19,54; 144,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,86; -7,36</t>
+          <t>38,02; 131,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -6,9</t>
+          <t>44,23; 150,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 3,89</t>
+          <t>-29,8; 85,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/BARTHEL_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>125,12%</t>
+          <t>149,74%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 9,94</t>
+          <t>-15,17; 9,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 47,73</t>
+          <t>12,17; 47,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 30,62</t>
+          <t>-7,97; 31,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 16,01</t>
+          <t>-0,22; 15,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,73; 572,15</t>
+          <t>43,94; 637,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 196,45</t>
+          <t>-25,27; 189,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 804,4</t>
+          <t>-13,71; 997,1</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,61</t>
+          <t>16,45</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>131,25%</t>
+          <t>141,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 17,93</t>
+          <t>0,78; 18,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 31,33</t>
+          <t>4,48; 32,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 26,16</t>
+          <t>6,59; 26,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 24,42</t>
+          <t>7,69; 25,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 1140,25</t>
+          <t>-12,56; 1229,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 346,46</t>
+          <t>14,03; 370,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,75; 752,58</t>
+          <t>43,15; 972,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,91; 379,98</t>
+          <t>43,29; 412,42</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 17,52</t>
+          <t>-3,26; 17,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 20,21</t>
+          <t>-8,79; 19,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 13,71</t>
+          <t>-7,56; 12,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 11,69</t>
+          <t>-7,0; 12,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,87; —</t>
+          <t>-40,77; 935,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 238,83</t>
+          <t>-39,94; 235,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 447,02</t>
+          <t>-69,91; 336,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 61,58</t>
+          <t>-24,88; 72,16</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>11,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>115,23%</t>
+          <t>130,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 21,17</t>
+          <t>0,94; 21,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 22,39</t>
+          <t>-2,2; 23,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 18,86</t>
+          <t>-7,2; 19,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 17,26</t>
+          <t>4,25; 18,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 1248,08</t>
+          <t>-17,01; 1273,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 321,49</t>
+          <t>-13,45; 341,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 187,01</t>
+          <t>-35,32; 172,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 293,96</t>
+          <t>29,0; 366,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,5</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 20,97</t>
+          <t>-13,98; 22,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 28,08</t>
+          <t>-13,48; 27,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 31,78</t>
+          <t>5,07; 31,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 15,86</t>
+          <t>-5,15; 16,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,98; 252,13</t>
+          <t>-56,81; 302,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 305,25</t>
+          <t>-43,63; 286,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,67; —</t>
+          <t>13,39; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 154,35</t>
+          <t>-23,3; 161,56</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 17,3</t>
+          <t>-5,29; 17,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 19,13</t>
+          <t>-12,63; 18,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 27,39</t>
+          <t>-3,57; 28,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 19,18</t>
+          <t>1,37; 20,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 662,16</t>
+          <t>-55,28; 753,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 130,66</t>
+          <t>-41,26; 129,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 195,21</t>
+          <t>-17,6; 238,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 114,53</t>
+          <t>3,03; 122,14</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>12,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-19,21%</t>
+          <t>112,13%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 5,39</t>
+          <t>-5,03; 4,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 16,6</t>
+          <t>-3,56; 17,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 23,62</t>
+          <t>5,21; 25,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 15,15</t>
+          <t>5,59; 21,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-81,93; 479,41</t>
+          <t>-80,46; 279,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 176,81</t>
+          <t>-19,66; 193,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,39; 282,96</t>
+          <t>25,91; 304,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 146,38</t>
+          <t>33,33; 271,06</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>109,69%</t>
+          <t>106,46%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 14,69</t>
+          <t>-4,13; 14,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 19,01</t>
+          <t>1,97; 19,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 12,57</t>
+          <t>-3,17; 13,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,62</t>
+          <t>4,09; 14,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 189,01</t>
+          <t>-23,16; 156,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,77; 376,72</t>
+          <t>8,36; 429,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 258,66</t>
+          <t>-30,77; 247,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,36; 251,65</t>
+          <t>28,46; 235,1</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>10,38</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,99</t>
+          <t>2,41; 9,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,74</t>
+          <t>6,34; 15,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,94; 14,47</t>
+          <t>5,36; 13,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,68</t>
+          <t>7,29; 13,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,54; 144,47</t>
+          <t>23,43; 143,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,02; 131,05</t>
+          <t>35,77; 131,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,23; 150,4</t>
+          <t>38,08; 131,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 85,63</t>
+          <t>51,57; 120,48</t>
         </is>
       </c>
     </row>
